--- a/results/job_matches_2026-05-26.xlsx
+++ b/results/job_matches_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform (Canada)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbaba31adfd57a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f80cce2b9ebf257</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer 5.5</t>
+          <t>Senior Software Engineer, Data Platform (Canada)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34da685bfe797839</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddbaba31adfd57a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab18efde0a1dd056</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4614253463977</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Middle–Senior Data Engineer with AI Experience</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DataArt</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b061d0e56606ca49</t>
+          <t>https://www.indeed.com/viewjob?jk=ab18efde0a1dd056</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Middle–Senior Data Engineer with AI Experience</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>DataArt</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae715a338ce50c4</t>
+          <t>https://www.indeed.com/viewjob?jk=b061d0e56606ca49</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=820e575795c52a30</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae715a338ce50c4</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1230,6 +1230,41 @@
         </is>
       </c>
       <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=820e575795c52a30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Vulcan Elements</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=48faa92f2e29036f</t>
         </is>

--- a/results/job_matches_2026-05-26.xlsx
+++ b/results/job_matches_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Integration Specialist</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Trauma Healing Accelerated</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa7b42d068847f61</t>
+          <t>https://www.indeed.com/viewjob?jk=36b655d5786f6e9c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>AI Integration Specialist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Trauma Healing Accelerated</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd329279eb0cbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=fa7b42d068847f61</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5397e30a285245d</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd329279eb0cbc5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8ea8730e4cf117</t>
+          <t>https://www.indeed.com/viewjob?jk=f5397e30a285245d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Native Developer</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbc661e109c14228</t>
+          <t>https://www.indeed.com/viewjob?jk=0a8ea8730e4cf117</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>AI Native Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bc77d9dc22a6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=dbc661e109c14228</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0214499e127c894</t>
+          <t>https://www.indeed.com/viewjob?jk=37bc77d9dc22a6a9</t>
         </is>
       </c>
     </row>
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad88277e472de1e</t>
+          <t>https://www.indeed.com/viewjob?jk=c0214499e127c894</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Native Developer</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba608063466f07bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad88277e472de1e</t>
         </is>
       </c>
     </row>
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36ab7b1b575050e1</t>
+          <t>https://www.indeed.com/viewjob?jk=ba608063466f07bd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>AI Native Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc95b3c395886fe7</t>
+          <t>https://www.indeed.com/viewjob?jk=36ab7b1b575050e1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Referral Only - Senior GCP Data Engineer</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b715538a1026e4</t>
+          <t>https://www.indeed.com/viewjob?jk=dc95b3c395886fe7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Referral Only - Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0866a3cb6383e0de</t>
+          <t>https://www.indeed.com/viewjob?jk=45b715538a1026e4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer @ Hybrid</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NextRow Digital</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, ECS, RDS, Snowflake, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e5c91036a8e42a</t>
+          <t>https://www.indeed.com/viewjob?jk=0866a3cb6383e0de</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Full Stack Software Engineer @ Hybrid</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NextRow Digital</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, ECS, RDS, Snowflake, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f80cce2b9ebf257</t>
+          <t>https://www.indeed.com/viewjob?jk=a3e5c91036a8e42a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform (Canada)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbaba31adfd57a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f80cce2b9ebf257</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Senior Software Engineer, Data Platform (Canada)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4614253463977</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddbaba31adfd57a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Scala, Oracle, DynamoDB, NoSQL, ETL, dbt, Tableau, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab18efde0a1dd056</t>
+          <t>https://www.indeed.com/viewjob?jk=716c39142598395c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Middle–Senior Data Engineer with AI Experience</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DataArt</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b061d0e56606ca49</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4614253463977</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae715a338ce50c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ab18efde0a1dd056</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Middle–Senior Data Engineer with AI Experience</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>DataArt</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,42 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=820e575795c52a30</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Vulcan Elements</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48faa92f2e29036f</t>
+          <t>https://www.indeed.com/viewjob?jk=b061d0e56606ca49</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-26.xlsx
+++ b/results/job_matches_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,12 +538,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Integration Specialist</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Trauma Healing Accelerated</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa7b42d068847f61</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd329279eb0cbc5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd329279eb0cbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=f5397e30a285245d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5397e30a285245d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a8ea8730e4cf117</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>AI Native Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8ea8730e4cf117</t>
+          <t>https://www.indeed.com/viewjob?jk=dbc661e109c14228</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Native Developer</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbc661e109c14228</t>
+          <t>https://www.indeed.com/viewjob?jk=37bc77d9dc22a6a9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bc77d9dc22a6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c0214499e127c894</t>
         </is>
       </c>
     </row>
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0214499e127c894</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad88277e472de1e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>AI Native Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad88277e472de1e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba608063466f07bd</t>
         </is>
       </c>
     </row>
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba608063466f07bd</t>
+          <t>https://www.indeed.com/viewjob?jk=36ab7b1b575050e1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Native Developer</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36ab7b1b575050e1</t>
+          <t>https://www.indeed.com/viewjob?jk=dc95b3c395886fe7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>BI Solutions Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc95b3c395886fe7</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa071bc6a31ae41</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Referral Only - Senior GCP Data Engineer</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,77 +941,77 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b715538a1026e4</t>
+          <t>https://www.indeed.com/viewjob?jk=960f767365c3fdc0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Allruva Technology Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Vertex AI, Spark, Scala, Spark Streaming, Kafka, MLOps</t>
+          <t>RDS, Databricks, Hadoop, HDFS, Hive, MapReduce, HBase, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0866a3cb6383e0de</t>
+          <t>https://www.indeed.com/viewjob?jk=a3fc6d4b0669cc2e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer @ Hybrid</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NextRow Digital</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, ECS, RDS, Snowflake, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e5c91036a8e42a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f80cce2b9ebf257</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer, Data Platform (Canada)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f80cce2b9ebf257</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddbaba31adfd57a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform (Canada)</t>
+          <t>Snowflake Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbaba31adfd57a</t>
+          <t>https://www.indeed.com/viewjob?jk=002369ff092a4302</t>
         </is>
       </c>
     </row>
@@ -1203,35 +1203,70 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Middle–Senior Data Engineer with AI Experience</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DataArt</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b061d0e56606ca49</t>
+          <t>https://www.indeed.com/viewjob?jk=2e887fffa7d23b98</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Backend</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Finalcover LLC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=254d43c61e4dbbb4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-26.xlsx
+++ b/results/job_matches_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Klaxon Technolgies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.4</v>
+        <v>39.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, API Gateway, RDS</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c207b60a85c3ae78</t>
+          <t>https://www.indeed.com/viewjob?jk=3265598d80fd8a76</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Senior Data Engineer, Platform Data</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Leadfeeder</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Athena, S3, ECS, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36b655d5786f6e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=d2b659aa81b3c306</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,94 +566,94 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd329279eb0cbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=36b655d5786f6e9c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>AI Solution Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Origence</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5397e30a285245d</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8da60d668640f5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Senior SRE I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8ea8730e4cf117</t>
+          <t>https://www.indeed.com/viewjob?jk=f88f8686e04e6680</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Native Developer</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,24 +661,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbc661e109c14228</t>
+          <t>https://www.indeed.com/viewjob?jk=196506204c7c944f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bc77d9dc22a6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd329279eb0cbc5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0214499e127c894</t>
+          <t>https://www.indeed.com/viewjob?jk=f5397e30a285245d</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad88277e472de1e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a8ea8730e4cf117</t>
         </is>
       </c>
     </row>
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba608063466f07bd</t>
+          <t>https://www.indeed.com/viewjob?jk=dbc661e109c14228</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Native Developer</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36ab7b1b575050e1</t>
+          <t>https://www.indeed.com/viewjob?jk=37bc77d9dc22a6a9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -881,137 +881,137 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc95b3c395886fe7</t>
+          <t>https://www.indeed.com/viewjob?jk=c0214499e127c894</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BI Solutions Architect</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa071bc6a31ae41</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad88277e472de1e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>AI Native Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=960f767365c3fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba608063466f07bd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>AI Native Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Allruva Technology Services</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, HDFS, Hive, MapReduce, HBase, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3fc6d4b0669cc2e</t>
+          <t>https://www.indeed.com/viewjob?jk=36ab7b1b575050e1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f80cce2b9ebf257</t>
+          <t>https://www.indeed.com/viewjob?jk=dc95b3c395886fe7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform (Canada)</t>
+          <t>BI Solutions Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbaba31adfd57a</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa071bc6a31ae41</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Snowflake Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=002369ff092a4302</t>
+          <t>https://www.indeed.com/viewjob?jk=4b965cc65d75bb68</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, DynamoDB, NoSQL, ETL, dbt, Tableau, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,102 +1126,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716c39142598395c</t>
+          <t>https://www.indeed.com/viewjob?jk=960f767365c3fdc0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Senior Development Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Business Information Group, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4614253463977</t>
+          <t>https://www.indeed.com/viewjob?jk=1790d3f21cf2701e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>Allruva Technology Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Databricks, Hadoop, HDFS, Hive, MapReduce, HBase, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab18efde0a1dd056</t>
+          <t>https://www.indeed.com/viewjob?jk=a3fc6d4b0669cc2e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Macmillan Publishers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, Power BI, Git</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,40 +1231,600 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e887fffa7d23b98</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb1d2668d2c3bb3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f80cce2b9ebf257</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer II (Remote, US)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openly</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4c0d71f6d3e3d52</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Platform (Canada)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TRM Labs</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ddbaba31adfd57a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Always Compassionate Health</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Melville, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e602a7ae37682d44</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Snowflake Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Smart Tech Skills LLC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=002369ff092a4302</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, Scala, Oracle, DynamoDB, NoSQL, ETL, dbt, Tableau, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=716c39142598395c</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Engineer II – Data Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3de4614253463977</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TeraWatt Infrastructure</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab18efde0a1dd056</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Java/Python</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e901ac4878117ce6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Forward Deployed Engineer - QuantumBlack, AI by McKinsey</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99421b7cddeacb9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, App</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Lila Sciences</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca392fa39b84631e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, App</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Lila Sciences</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f024bf694f893ebe</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fustis LLC</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>El Paso, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e887fffa7d23b98</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Recutify Inc.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ee880f838d01800</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Lila Sciences</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b975973860fe466c</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Lila Sciences</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b47adc71ffc989c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Senior Software Engineer – Backend</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Finalcover LLC</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Arlington, VA, US USA</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D40" t="n">
         <v>10.4</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=254d43c61e4dbbb4</t>
         </is>

--- a/results/job_matches_2026-05-26.xlsx
+++ b/results/job_matches_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,69 +556,69 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36b655d5786f6e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=366df588234a7c92</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Solution Architect</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Origence</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8da60d668640f5</t>
+          <t>https://www.indeed.com/viewjob?jk=36b655d5786f6e9c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior SRE I</t>
+          <t>AI Solution Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Origence</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, GCP, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f88f8686e04e6680</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8da60d668640f5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer, I - Data Engineering</t>
+          <t>Senior SRE I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=196506204c7c944f</t>
+          <t>https://www.indeed.com/viewjob?jk=f88f8686e04e6680</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,24 +696,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd329279eb0cbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=196506204c7c944f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5397e30a285245d</t>
+          <t>https://www.indeed.com/viewjob?jk=bcd329279eb0cbc5</t>
         </is>
       </c>
     </row>
@@ -1028,25 +1028,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BI Solutions Architect</t>
+          <t>Controllers, Software Engineering, Salt Lake City, Associate</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa071bc6a31ae41</t>
+          <t>https://www.indeed.com/viewjob?jk=81361a25f18bfa9e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>BI Solutions Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b965cc65d75bb68</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa071bc6a31ae41</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=960f767365c3fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=4b965cc65d75bb68</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Development Consultant</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Business Information Group, Inc.</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1790d3f21cf2701e</t>
+          <t>https://www.indeed.com/viewjob?jk=960f767365c3fdc0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Software Engineer III, Voice AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Allruva Technology Services</t>
+          <t>Natera</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, HDFS, Hive, MapReduce, HBase, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Azure, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3fc6d4b0669cc2e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff57ba86e213734</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>2026012 - Senior Software Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Macmillan Publishers</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb1d2668d2c3bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=59907092ed75df82</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f80cce2b9ebf257</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b056aa8ae1df1b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II (Remote, US)</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>Allruva Technology Services</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Databricks, Hadoop, HDFS, Hive, MapReduce, HBase, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c0d71f6d3e3d52</t>
+          <t>https://www.indeed.com/viewjob?jk=a3fc6d4b0669cc2e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform (Canada)</t>
+          <t>Copy of Senior Data Engineer (Azure &amp; Databricks)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbaba31adfd57a</t>
+          <t>https://www.indeed.com/viewjob?jk=634ea8c9beab0812</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Senior Data Engineer (Azure &amp; Databricks)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Always Compassionate Health</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e602a7ae37682d44</t>
+          <t>https://www.indeed.com/viewjob?jk=dd215d5414c53bc0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Snowflake Engineer</t>
+          <t>Senior Solutions Architect - Emerging Technologies (AI, GenAI, ML)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, ECS, Azure, Vertex AI, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=002369ff092a4302</t>
+          <t>https://www.indeed.com/viewjob?jk=21e1b2180a79f7cc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Prime Cargo People Logistics</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, DynamoDB, NoSQL, ETL, dbt, Tableau, Git, Bitbucket</t>
+          <t>AWS, Lambda, S3, ECS, RDS, GCP, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,102 +1441,102 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716c39142598395c</t>
+          <t>https://www.indeed.com/viewjob?jk=c504b34cabd6342d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Senior Engineer 2: AI Agentic Solutions (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4614253463977</t>
+          <t>https://www.indeed.com/viewjob?jk=d1942d9ec58e935c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>Macmillan Publishers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab18efde0a1dd056</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb1d2668d2c3bb3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II - Java/Python</t>
+          <t>Full Stack AI + Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Spark, Spark Streaming, Kafka, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e901ac4878117ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=6740052e5af1c2fe</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Engineer - QuantumBlack, AI by McKinsey</t>
+          <t>2026011 - Operations Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99421b7cddeacb9e</t>
+          <t>https://www.indeed.com/viewjob?jk=21cc17fa6fcb98f8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca392fa39b84631e</t>
+          <t>https://www.indeed.com/viewjob?jk=9f80cce2b9ebf257</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, App</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f024bf694f893ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=1985124aab93f8b5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e887fffa7d23b98</t>
+          <t>https://www.indeed.com/viewjob?jk=b50977d506f8a126</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Site Reliability Engineer II (Remote, US)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes, CloudWatch</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ee880f838d01800</t>
+          <t>https://www.indeed.com/viewjob?jk=c4c0d71f6d3e3d52</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Software Engineer, Data Platform (Canada)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975973860fe466c</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddbaba31adfd57a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>Always Compassionate Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,40 +1791,565 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47adc71ffc989c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e602a7ae37682d44</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Snowflake Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Smart Tech Skills LLC</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=002369ff092a4302</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, Scala, Oracle, DynamoDB, NoSQL, ETL, dbt, Tableau, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=716c39142598395c</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Engineer II – Data Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3de4614253463977</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TeraWatt Infrastructure</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab18efde0a1dd056</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Kinsale Management Inc</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a938739108dd1870</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Java/Python</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e901ac4878117ce6</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Quanex</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f22e7be74451275b</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Cloud Data Platform</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Informatica PowerCenter, Data Modeling, ETL, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de80a4e1ea3c7456</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Forward Deployed Engineer - QuantumBlack, AI by McKinsey</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99421b7cddeacb9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, App</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Lila Sciences</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca392fa39b84631e</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, App</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Lila Sciences</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f024bf694f893ebe</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e70cddc4d406c6fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Lila Sciences</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b975973860fe466c</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Lila Sciences</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b47adc71ffc989c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Recutify Inc.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ee880f838d01800</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Senior Software Engineer – Backend</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Finalcover LLC</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Arlington, VA, US USA</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D55" t="n">
         <v>10.4</v>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=254d43c61e4dbbb4</t>
         </is>

--- a/results/job_matches_2026-05-26.xlsx
+++ b/results/job_matches_2026-05-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior SRE I</t>
+          <t>Software Engineer, I - Data Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f88f8686e04e6680</t>
+          <t>https://www.indeed.com/viewjob?jk=196506204c7c944f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer, I - Data Engineering</t>
+          <t>Controllers, Software Engineering, Salt Lake City, Associate</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, ECS, Data Factory, Databricks, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,89 +706,89 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=196506204c7c944f</t>
+          <t>https://www.indeed.com/viewjob?jk=81361a25f18bfa9e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>BI Solutions Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcd329279eb0cbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=aaa071bc6a31ae41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8ea8730e4cf117</t>
+          <t>https://www.indeed.com/viewjob?jk=4b965cc65d75bb68</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Native Developer</t>
+          <t>Software Engineer III, Voice AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Natera</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,256 +797,256 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Azure, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbc661e109c14228</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff57ba86e213734</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Senior Agentic AI Architect/Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Polars, PostgreSQL, Azure Cosmos DB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bc77d9dc22a6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=cc83cb585d053a0f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0214499e127c894</t>
+          <t>https://www.indeed.com/viewjob?jk=960f767365c3fdc0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>2026012 - Senior Software Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad88277e472de1e</t>
+          <t>https://www.indeed.com/viewjob?jk=59907092ed75df82</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Native Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Quarterhill</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba608063466f07bd</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b056aa8ae1df1b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Native Developer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Allruva Technology Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Databricks, Hadoop, HDFS, Hive, MapReduce, HBase, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36ab7b1b575050e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a3fc6d4b0669cc2e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Copy of Senior Data Engineer (Azure &amp; Databricks)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc95b3c395886fe7</t>
+          <t>https://www.indeed.com/viewjob?jk=634ea8c9beab0812</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Controllers, Software Engineering, Salt Lake City, Associate</t>
+          <t>Senior Data Engineer (Azure &amp; Databricks)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81361a25f18bfa9e</t>
+          <t>https://www.indeed.com/viewjob?jk=dd215d5414c53bc0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BI Solutions Architect</t>
+          <t>Senior Solutions Architect - Emerging Technologies (AI, GenAI, ML)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, ECS, Azure, Vertex AI, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaa071bc6a31ae41</t>
+          <t>https://www.indeed.com/viewjob?jk=21e1b2180a79f7cc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Prime Cargo People Logistics</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, ECS, RDS, GCP, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b965cc65d75bb68</t>
+          <t>https://www.indeed.com/viewjob?jk=c504b34cabd6342d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Senior Engineer 2: AI Agentic Solutions (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=960f767365c3fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=d1942d9ec58e935c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III, Voice AI</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Natera</t>
+          <t>Macmillan Publishers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Azure, Scala, Kafka</t>
+          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff57ba86e213734</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb1d2668d2c3bb3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026012 - Senior Software Analyst</t>
+          <t>Full Stack AI + Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Techtorch</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Power BI, Tableau</t>
+          <t>AWS, Azure, Spark, Spark Streaming, Kafka, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59907092ed75df82</t>
+          <t>https://www.indeed.com/viewjob?jk=6740052e5af1c2fe</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>2026011 - Operations Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quarterhill</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b056aa8ae1df1b</t>
+          <t>https://www.indeed.com/viewjob?jk=21cc17fa6fcb98f8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Allruva Technology Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, HDFS, Hive, MapReduce, HBase, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3fc6d4b0669cc2e</t>
+          <t>https://www.indeed.com/viewjob?jk=9f80cce2b9ebf257</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Copy of Senior Data Engineer (Azure &amp; Databricks)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634ea8c9beab0812</t>
+          <t>https://www.indeed.com/viewjob?jk=b50977d506f8a126</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure &amp; Databricks)</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>Chesapeake Utilities Corporation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd215d5414c53bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=1985124aab93f8b5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Emerging Technologies (AI, GenAI, ML)</t>
+          <t>Senior Software Engineer, Data Platform (Canada)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>TRM Labs</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Vertex AI, Scala, NoSQL, Data Modeling, MLOps, CI/CD, Terraform</t>
+          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21e1b2180a79f7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddbaba31adfd57a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Prime Cargo People Logistics</t>
+          <t>Always Compassionate Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, GCP, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c504b34cabd6342d</t>
+          <t>https://www.indeed.com/viewjob?jk=e602a7ae37682d44</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer 2: AI Agentic Solutions (Hybrid - Seattle, WA)</t>
+          <t>Snowflake Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, BigQuery, Spark, Scala, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1942d9ec58e935c</t>
+          <t>https://www.indeed.com/viewjob?jk=002369ff092a4302</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Macmillan Publishers</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Cloud Storage, Vertex AI, Scala, Snowflake, PostgreSQL, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Scala, Oracle, DynamoDB, NoSQL, ETL, dbt, Tableau, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,137 +1511,137 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb1d2668d2c3bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=716c39142598395c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack AI + Data Engineer</t>
+          <t>Engineer II – Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Techtorch</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Spark Streaming, Kafka, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6740052e5af1c2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3de4614253463977</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026011 - Operations Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21cc17fa6fcb98f8</t>
+          <t>https://www.indeed.com/viewjob?jk=ab18efde0a1dd056</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer II - Java/Python</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f80cce2b9ebf257</t>
+          <t>https://www.indeed.com/viewjob?jk=e901ac4878117ce6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chesapeake Utilities Corporation</t>
+          <t>Kinsale Management Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1985124aab93f8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=a938739108dd1870</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Butler Till</t>
+          <t>Quanex</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50977d506f8a126</t>
+          <t>https://www.indeed.com/viewjob?jk=f22e7be74451275b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II (Remote, US)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c0d71f6d3e3d52</t>
+          <t>https://www.indeed.com/viewjob?jk=877d45e3d1a625d6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform (Canada)</t>
+          <t>Senior Data Engineer - Cloud Data Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TRM Labs</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Informatica PowerCenter, Data Modeling, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbaba31adfd57a</t>
+          <t>https://www.indeed.com/viewjob?jk=de80a4e1ea3c7456</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer, Enterprise Data &amp; Analytics</t>
+          <t>Senior Forward Deployed Engineer - QuantumBlack, AI by McKinsey</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Always Compassionate Health</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e602a7ae37682d44</t>
+          <t>https://www.indeed.com/viewjob?jk=99421b7cddeacb9e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Snowflake Engineer</t>
+          <t>Senior Software Engineer, App</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=002369ff092a4302</t>
+          <t>https://www.indeed.com/viewjob?jk=ca392fa39b84631e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer, App</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, DynamoDB, NoSQL, ETL, dbt, Tableau, Git, Bitbucket</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,102 +1861,102 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716c39142598395c</t>
+          <t>https://www.indeed.com/viewjob?jk=f024bf694f893ebe</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Engineer II – Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3de4614253463977</t>
+          <t>https://www.indeed.com/viewjob?jk=7b8a567bdd35f252</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab18efde0a1dd056</t>
+          <t>https://www.indeed.com/viewjob?jk=e70cddc4d406c6fc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kinsale Management Inc</t>
+          <t>Nexstar Media Group, Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, DynamoDB, Data Modeling</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a938739108dd1870</t>
+          <t>https://www.indeed.com/viewjob?jk=7b532541851ceb06</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer II - Java/Python</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e901ac4878117ce6</t>
+          <t>https://www.indeed.com/viewjob?jk=2ee880f838d01800</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Quanex</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Oracle, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22e7be74451275b</t>
+          <t>https://www.indeed.com/viewjob?jk=b975973860fe466c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Cloud Data Platform</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Informatica PowerCenter, Data Modeling, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,287 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de80a4e1ea3c7456</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Senior Forward Deployed Engineer - QuantumBlack, AI by McKinsey</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>McKinsey &amp; Company</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99421b7cddeacb9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, App</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Lila Sciences</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca392fa39b84631e</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, App</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Lila Sciences</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f024bf694f893ebe</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e70cddc4d406c6fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Lila Sciences</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b975973860fe466c</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Lila Sciences</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow, Git, Python</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=b47adc71ffc989c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Recutify Inc.</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ee880f838d01800</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer – Backend</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Finalcover LLC</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=254d43c61e4dbbb4</t>
         </is>
       </c>
     </row>
